--- a/reports/pdf_change_20261015.xlsx
+++ b/reports/pdf_change_20261015.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,127억   ·   현금 88억(1.8%)      당일 2026-10-15  vs  전영업일 2026-10-14      매수 6종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,947억      당일 2026-10-15  vs  전영업일 2026-10-14      매수 6종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>242</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1647577639</v>
+        <v>1645913802</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-140</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1437346835</v>
+        <v>-1435895304</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>32</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1523762061</v>
+        <v>1522223262</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-48</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-851943138</v>
+        <v>-851082787</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1209714066</v>
+        <v>1208492414</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-39</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1109226636</v>
+        <v>-1108106463</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>962509041</v>
+        <v>961537034</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-29</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-477067544</v>
+        <v>-476585769</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1510086257</v>
+        <v>1508561269</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-25</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1414652928</v>
+        <v>-1413224315</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>960279291</v>
+        <v>959309535</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-474094544</v>
+        <v>-473615770</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-474490944</v>
+        <v>-474011770</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>-9</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1257579381</v>
+        <v>-1256309391</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-665159401</v>
+        <v>-664487678</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>-4</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-690529009</v>
+        <v>-689831666</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,017억   ·   현금 25억(0.8%)      당일 2026-10-15  vs  전영업일 2026-10-14      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,990억      당일 2026-10-15  vs  전영업일 2026-10-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1063,7 +1063,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,650억   ·   현금 41억(1.6%)      당일 2026-10-15  vs  전영업일 2026-10-14      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,556억      당일 2026-10-15  vs  전영업일 2026-10-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1087,7 +1087,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,933억   ·   현금 14억(0.7%)      당일 2026-10-15  vs  전영업일 2026-10-14      매수 2종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,913억      당일 2026-10-15  vs  전영업일 2026-10-14      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1183,7 +1183,7 @@
         <v>28</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1928175603</v>
+        <v>1928174999</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>-112</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-952291399</v>
+        <v>-952291101</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1810824378</v>
+        <v>1810823811</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>-22</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-3408317712</v>
+        <v>-3408316644</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억   ·   현금 3억(1.1%)      당일 2026-10-15  vs  전영업일 2026-10-14      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 296억      당일 2026-10-15  vs  전영업일 2026-10-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>

--- a/reports/pdf_change_20261015.xlsx
+++ b/reports/pdf_change_20261015.xlsx
@@ -839,23 +839,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1508561269</v>
+        <v>959309535</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.44%→1.81%</t>
+          <t>1.02%→1.19%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>92→111</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -883,23 +883,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>959309535</v>
+        <v>1508561269</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.19%</t>
+          <t>1.44%→1.81%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>92→111</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
